--- a/hospital/пол/hospital-floors.xlsx
+++ b/hospital/пол/hospital-floors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Ед. изм.</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>объем, м3.</t>
+  </si>
+  <si>
+    <t>м3</t>
   </si>
 </sst>
 </file>
@@ -206,6 +209,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -216,6 +222,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -226,18 +241,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -557,26 +560,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="17" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -590,11 +593,11 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="12"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="16"/>
       <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
@@ -610,16 +613,16 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="12"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16"/>
       <c r="E4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G4" s="4">
         <f>C9</f>
@@ -627,13 +630,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
@@ -645,10 +648,10 @@
       <c r="C6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
@@ -661,10 +664,10 @@
         <f>B7*0.089</f>
         <v>121.8588</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
@@ -677,10 +680,10 @@
         <f>B8*0.089</f>
         <v>118.9396</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -694,10 +697,10 @@
         <f>SUM(C7:C8)</f>
         <v>240.79840000000002</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/hospital/пол/hospital-floors.xlsx
+++ b/hospital/пол/hospital-floors.xlsx
@@ -4,17 +4,19 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1.1пл" sheetId="14" r:id="rId1"/>
+    <sheet name="1.2пл3в" sheetId="15" r:id="rId1"/>
+    <sheet name="1.3Инв" sheetId="16" r:id="rId2"/>
+    <sheet name="1.1Инв" sheetId="14" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="23">
   <si>
     <t>Ед. изм.</t>
   </si>
@@ -63,6 +65,28 @@
   </si>
   <si>
     <t>м3</t>
+  </si>
+  <si>
+    <t>Вид</t>
+  </si>
+  <si>
+    <t>Стяжка</t>
+  </si>
+  <si>
+    <t>Керамзит</t>
+  </si>
+  <si>
+    <t>1, 4, 5 этаж</t>
+  </si>
+  <si>
+    <t>1, 4, 5 этаж
+(89-90 мм)</t>
+  </si>
+  <si>
+    <t>Объем</t>
+  </si>
+  <si>
+    <t>Устройство стяжки СКБ / армированная сеткой до 40 мм</t>
   </si>
 </sst>
 </file>
@@ -189,7 +213,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -212,34 +236,58 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -547,6 +595,396 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4">
+        <f>B11</f>
+        <v>3518.32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4">
+        <f>C11</f>
+        <v>313.13047999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1291.9000000000001</v>
+      </c>
+      <c r="C8" s="4">
+        <f>B8*0.089</f>
+        <v>114.9791</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1317.1</v>
+      </c>
+      <c r="C9" s="4">
+        <f t="shared" ref="C9:C10" si="0">B9*0.089</f>
+        <v>117.22189999999999</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4">
+        <v>909.32</v>
+      </c>
+      <c r="C10" s="4">
+        <f t="shared" si="0"/>
+        <v>80.929479999999998</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4">
+        <f>SUM(B8:B10)</f>
+        <v>3518.32</v>
+      </c>
+      <c r="C11" s="4">
+        <f>SUM(C8:C10)</f>
+        <v>313.13047999999998</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="D6:G11"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="7.77734375" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:7" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4">
+        <f>B10</f>
+        <v>3518.32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4">
+        <f>C10</f>
+        <v>313.13047999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1291.9000000000001</v>
+      </c>
+      <c r="C7" s="4">
+        <v>114.9791</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1317.1</v>
+      </c>
+      <c r="C8" s="4">
+        <v>117.22189999999999</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4">
+        <v>909.32</v>
+      </c>
+      <c r="C9" s="4">
+        <v>80.929479999999998</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4">
+        <f>SUM(B7:B9)</f>
+        <v>3518.32</v>
+      </c>
+      <c r="C10" s="4">
+        <f>SUM(C7:C9)</f>
+        <v>313.13047999999998</v>
+      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="D6:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -560,25 +998,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="13"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
@@ -593,11 +1031,11 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
       <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
@@ -613,11 +1051,11 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="16"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
       <c r="E4" s="3" t="s">
         <v>13</v>
       </c>
@@ -630,13 +1068,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
@@ -648,10 +1086,10 @@
       <c r="C6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
@@ -664,10 +1102,10 @@
         <f>B7*0.089</f>
         <v>121.8588</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
@@ -680,10 +1118,10 @@
         <f>B8*0.089</f>
         <v>118.9396</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -697,10 +1135,10 @@
         <f>SUM(C7:C8)</f>
         <v>240.79840000000002</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">
